--- a/aq_files/0085.xlsx
+++ b/aq_files/0085.xlsx
@@ -1,98 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dataset" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
-  <si>
-    <t>A researcher divides a city into blocks and randomly selects a few blocks, then surveys all households in those blocks. What sampling method is used?</t>
-  </si>
-  <si>
-    <t>A school district randomly selects a few schools and surveys all students in those selected schools. Identify the sampling technique.</t>
-  </si>
-  <si>
-    <t>A country is divided into regions, and a few regions are randomly chosen. All individuals in those regions are surveyed. What type of sampling is this?</t>
-  </si>
-  <si>
-    <t>A company selects a few branches randomly and surveys all employees in those branches. What sampling method is applied?</t>
-  </si>
-  <si>
-    <t>A researcher divides a population into villages and randomly selects some villages to study all residents. Identify the sampling method.</t>
-  </si>
-  <si>
-    <t>A university randomly selects a few classes and surveys all students in those classes. What type of sampling is used?</t>
-  </si>
-  <si>
-    <t>A health survey randomly selects hospitals and studies all patients in those hospitals. What sampling method is this?</t>
-  </si>
-  <si>
-    <t>A researcher selects a few apartment buildings randomly and surveys all residents in those buildings. Identify the sampling type.</t>
-  </si>
-  <si>
-    <t>A company randomly selects warehouses and inspects all products in those warehouses. What sampling method is used?</t>
-  </si>
-  <si>
-    <t>A government survey randomly selects districts and collects data from all households within those districts. Identify the sampling technique.</t>
-  </si>
-  <si>
-    <t>A study divides a population into clusters based on geographic areas and randomly selects some areas for full data collection. What type of sampling is this?</t>
-  </si>
-  <si>
-    <t>A researcher randomly selects a few classrooms and surveys every student in those classrooms. Identify the sampling method.</t>
-  </si>
-  <si>
-    <t>A city is divided into wards, and a few wards are randomly chosen. All people in selected wards are surveyed. What sampling method is used?</t>
-  </si>
-  <si>
-    <t>A company selects a few retail stores randomly and surveys all customers visiting those stores. Identify the sampling type.</t>
-  </si>
-  <si>
-    <t>A research team randomly selects a few factories and studies all workers in those factories. What sampling method is this?</t>
-  </si>
-  <si>
-    <t>A country survey selects a few states randomly and collects data from all residents in those states. Identify the sampling method.</t>
-  </si>
-  <si>
-    <t>A researcher selects a few office buildings randomly and surveys all employees in those buildings. What type of sampling is used?</t>
-  </si>
-  <si>
-    <t>A school board randomly selects some sections and surveys all students in those sections. Identify the sampling method.</t>
-  </si>
-  <si>
-    <t>A researcher divides the population into clusters and randomly selects a few clusters, but surveys only some individuals within those clusters. What type of sampling is this?</t>
-  </si>
-  <si>
-    <t>A survey selects districts, then schools within those districts, and finally students within those schools. What type of sampling approach is this?</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
-      <sz val="10.0"/>
+      <name val="Arial"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <sz val="10"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Arial"/>
       <color theme="1"/>
-      <name val="Arial"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="lightGray"/>
@@ -102,29 +39,86 @@
     <border/>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -322,113 +316,978 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:B51"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Row_ID,Product_Name,Product_Code,Email_Address,Order_Date,Sales_Amount,Quantity,Unit_Price,Discount,Region,City,State,Full_Name,Address,Product_Description,Transaction_Code,Customer_Feedback,Website_URL,File_Name,ID_Number</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>Question Type</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>1,MacBook Pro 16-inch M3 Pro,MBP-16-2024,john.smith@email.com,2024-01-05,1299.99,1,1299.99,0.05,North,Chicago,Illinois,Smith, John,123 Main St,Chicago IL 60601,"Apple MacBook Pro 16-inch with M3 Pro chip, 18GB RAM, 512GB SSD",TRX-2024-001-USA,Excellent product! Fast shipping,https://www.apple.com/macbook-pro/,sales_report_2024_01_05.csv,ID-001-ABC-2024</t>
+        </is>
+      </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>2,Magic Mouse Wireless,MMW-2024-002,jane.doe@company.com,2024-01-05,79.99,3,26.66,0.10,North,Chicago,Illinois,Doe, Jane,456 Oak Ave,Chicago IL 60602,"Magic Mouse Wireless, rechargeable, multi-touch surface",TRX-2024-002-USA,Works great with my Mac,https://www.apple.com/magic-mouse/,sales_report_2024_01_05.csv,ID-002-DEF-2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>3,Designer Jeans Blue,DJB-2024-003,robert.wilson@email.ca,2024-01-06,89.99,2,44.99,0.00,South,Houston,Texas,Wilson, Robert,789 Pine St,Houston TX 77001,"Premium designer jeans, slim fit, dark blue",TRX-2024-003-CAN,Perfect fit, love the color,https://www.levi.com/jeans/,january_sales_2024.csv,ID-003-GHI-2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>4,27-inch 4K Monitor,4KM-2024-004,sarah.johnson@email.com,2024-01-06,299.99,1,299.99,0.15,South,Austin,Texas,Johnson, Sarah,321 Elm St,Austin TX 78701,"27-inch 4K UHD Monitor, IPS panel, 144Hz refresh rate",TRX-2024-004-USA,Amazing picture quality,https://www.dell.com/monitors/,january_sales_2024.csv,ID-004-JKL-2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>5,Executive Leather Chair,ELC-2024-005,michael.brown@email.co.uk,2024-01-07,399.99,2,199.99,0.05,East,New York,New York,Brown, Michael,654 Maple Ave,New York NY 10001,"Executive office chair, genuine leather, ergonomic design",TRX-2024-005-UK,Very comfortable, good quality,https://www.hermanmiller.com/chairs/,february_sales_2024.csv,ID-005-MNO-2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>6,Mechanical RGB Keyboard,MRK-2024-006,lisa.anderson@email.com.au,2024-01-07,89.99,2,44.99,0.10,West,Los Angeles,California,Anderson, Lisa,987 Cedar Ln,Los Angeles CA 90001,"Mechanical keyboard, RGB backlight, blue switches",TRX-2024-006-AUS,Great for gaming,https://www.corsair.com/keyboards/,february_sales_2024.csv,ID-006-PQR-2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>7,Leather Jacket Black,LJB-2024-007,robert.taylor@email.com,2024-01-08,199.99,1,199.99,0.20,West,San Diego,California,Taylor, Robert,147 Birch St,San Diego CA 92101,"Genuine leather jacket, classic biker style, black",TRX-2024-007-USA,Looks stylish, good quality,https://www.zara.com/jackets/,march_sales_2024.csv,ID-007-STU-2024</t>
+        </is>
+      </c>
+      <c r="B8" s="0" t="inlineStr">
+        <is>
+          <t>Coding</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>8,iPad Pro 12.9-inch,IPP-2024-008,jennifer.martinez@email.de,2024-01-08,499.99,1,499.99,0.05,East,Boston,Massachusetts,Martinez, Jennifer,258 Spruce Ave,Boston MA 02101,"iPad Pro 12.9-inch, M2 chip, 256GB storage, Wi-Fi + Cellular",TRX-2024-008-GER,Best tablet ever,https://www.apple.com/ipad-pro/,march_sales_2024.csv,ID-008-VWX-2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>9,Floor Lamp Modern,FLM-2024-009,richard.moore@email.fr,2024-01-09,79.99,2,39.99,0.00,North,Detroit,Michigan,Moore, Richard,369 Walnut St,Detroit MI 48201,"Modern floor lamp, adjustable height, LED compatible",TRX-2024-009-FRA,Good value for money,https://www.ikea.com/lighting/,april_sales_2024.csv,ID-009-YZA-2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>10,Running Shoes Pro,RSP-2024-010,linda.wilson@email.com,2024-01-09,69.99,1,69.99,0.10,South,Dallas,Texas,Wilson, Linda,741 Cherry Ln,Dallas TX 75201,"Professional running shoes, cushioned sole, breathable mesh",TRX-2024-010-USA,Very comfortable,https://www.nike.com/shoes/,april_sales_2024.csv,ID-010-BCD-2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>11,Gaming Laptop RTX,GLP-2024-011,patricia.davis@email.ca,2024-01-10,1299.99,1,1299.99,0.15,West,Seattle,Washington,Davis, Patricia,852 Dogwood Dr,Seattle WA 98101,"Gaming laptop, RTX 4060, 16GB RAM, 1TB SSD, 144Hz display",TRX-2024-011-CAN,Amazing performance,https://www.asus.com/laptops/,may_sales_2024.csv,ID-011-EFG-2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12,Wireless Headphones,WNH-2024-012,michael.miller@email.co.uk,2024-01-10,149.99,2,74.99,0.05,East,Philadelphia,Pennsylvania,Miller, Michael,951 Fir Ln,Philadelphia PA 19101,"Noise cancelling wireless headphones, 30-hour battery",TRX-2024-012-UK,Great sound quality,https://www.sony.com/headphones/,may_sales_2024.csv,ID-012-HIJ-2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>13,Wool Winter Coat,WWC-2024-013,jessica.thomas@email.com,2024-01-11,189.99,1,189.99,0.20,West,Portland,Oregon,Thomas, Jessica,753 Poplar Ave,Portland OR 97201,"Warm wool coat, classic design, camel color",TRX-2024-013-USA,Very warm and stylish,https://www.nordstrom.com/coats/,june_sales_2024.csv,ID-013-KLM-2024</t>
+        </is>
+      </c>
+      <c r="B14" s="0" t="inlineStr">
+        <is>
+          <t>Coding</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>14,5-Tier Oak Bookshelf,BOO-2024-014,sarah.white@email.com.au,2024-01-11,159.99,1,159.99,0.10,North,Columbus,Ohio,White, Sarah,159 Cypress Ct,Columbus OH 43201,"Solid oak bookshelf, 5 adjustable shelves, 72 inches tall",TRX-2024-014-AUS,Sturdy and looks great,https://www.wayfair.com/furniture/,june_sales_2024.csv,ID-014-NOP-2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>15,Smartphone Pro Max,SPM-2024-015,james.walker@email.de,2024-01-12,699.99,2,349.99,0.05,South,Miami,Florida,Walker, James,357 Willow Dr,Miami FL 33101,"Latest smartphone, 6.7-inch display, triple camera, 5G",TRX-2024-015-GER,Best phone I've owned,https://www.samsung.com/phones/,july_sales_2024.csv,ID-015-QRS-2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>16,Dress Shirt Formal,DSF-2024-016,thomas.anderson@email.fr,2024-01-12,59.99,3,20.00,0.00,East,Pittsburgh,Pennsylvania,Anderson, Thomas,951 Magnolia Rd,Pittsburgh PA 15201,"Formal dress shirt, 100% cotton, wrinkle-free, white",TRX-2024-016-FRA,Great fit, good quality,https://www.brooksbrothers.com/shirts/,july_sales_2024.csv,ID-016-TUV-2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>17,External SSD 1TB,ESS-2024-017,charles.jackson@email.com,2024-01-13,99.99,1,99.99,0.10,West,San Jose,California,Jackson, Charles,753 Ash St,San Jose CA 95101,"External SSD, 1TB capacity, USB-C, 1000MB/s read speed",TRX-2024-017-USA,Very fast transfer,https://www.samsung.com/storage/,august_sales_2024.csv,ID-017-WXY-2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>18,Cotton Hoodie Gray,CHG-2024-018,daniel.harris@email.ca,2024-01-13,49.99,2,25.00,0.05,North,Indianapolis,Indiana,Harris, Daniel,159 Beech Ct,Indianapolis IN 46201,"Cotton hoodie, gray, comfortable fit, kangaroo pocket",TRX-2024-018-CAN,Very comfortable,https://www.gap.com/hoodies/,august_sales_2024.csv,ID-018-ZAB-2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>19,Gaming Desk RGB,GDR-2024-019,edward.king@email.co.uk,2024-01-14,349.99,1,349.99,0.15,South,Atlanta,Georgia,King, Edward,357 Cedar Ave,Atlanta GA 30301,"Gaming desk, RGB lighting, carbon fiber surface, height adjustable",TRX-2024-019-UK,Perfect for gaming setup,https://www.razer.com/desks/,september_sales_2024.csv,ID-019-CDE-2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>20,4K Webcam Pro,4KW-2024-020,betty.hall@email.com,2024-01-14,79.99,2,39.99,0.10,East,Rochester,New York,Hall, Betty,753 Palm Ave,Rochester NY 14601,"4K webcam, autofocus, dual microphone, privacy cover",TRX-2024-020-USA,Clear video quality,https://www.logitech.com/webcams/,september_sales_2024.csv,ID-020-FGH-2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>21,Thunderbolt Dock,TBD-2024-021,kevin.young@email.com.au,2024-02-01,129.99,1,129.99,0.00,West,Denver,Colorado,Young, Kevin,951 Elm Dr,Denver CO 80201,"Thunderbolt 4 dock, 7-in-1, 85W power delivery, HDMI 2.1",TRX-2024-021-AUS,Works perfectly,https://www.caldigit.com/docks/,october_sales_2024.csv,ID-021-IJK-2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>22,Winter Parka Black,WPB-2024-022,nancy.allen@email.de,2024-02-01,179.99,1,179.99,0.05,North,Minneapolis,Minnesota,Allen, Nancy,753 Oak Ct,Minneapolis MN 55401,"Winter parka, insulated, waterproof, hooded, black",TRX-2024-022-GER,Keeps me very warm,https://www.thenorthface.com/jackets/,october_sales_2024.csv,ID-022-LMN-2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>23,Office Desk Walnut,ODW-2024-023,donna.wright@email.fr,2024-02-02,449.99,1,449.99,0.10,South,Orlando,Florida,Wright, Donna,159 Pine St,Orlando FL 32801,"Office desk, walnut finish, 60x30 inches, standing desk",TRX-2024-023-FRA,Beautiful desk,https://www.fully.com/desks/,november_sales_2024.csv,ID-023-OPQ-2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>24,USB-C Hub 7-in-1,UCH-2024-024,kimberly.carter@email.com,2024-02-02,39.99,3,13.33,0.00,East,Newark,New Jersey,Carter, Kimberly,357 Spruce Ln,Newark NJ 07101,"USB-C hub, 7 ports, HDMI, Ethernet, SD card reader, USB 3.0",TRX-2024-024-USA,Very useful accessory,https://www.anker.com/hubs/,november_sales_2024.csv,ID-024-RST-2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>25,Casual Blazer Navy,CBN-2024-025,george.lopez@email.ca,2024-02-03,149.99,1,149.99,0.15,West,Albuquerque,New Mexico,Lopez, George,951 Walnut Ave,Albuquerque NM 87101,"Casual blazer, navy, wool blend, single-breasted",TRX-2024-025-CAN,Looks very sharp,https://www.hm.com/blazers/,december_sales_2024.csv,ID-025-UVW-2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>26,ORD-1026,2024-02-03,59.99,2,17.99,0.10,Electronics,Gaming Mouse,22,Consumer,Medium,2,Returned,TRUE,2.9,2,29.99,8.50,COD</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>27,ORD-1027,2024-02-04,199.99,1,59.99,0.05,Electronics,Laser Printer,49,Corporate,High,4,Delivered,FALSE,4.8,1,199.99,18.00,Net30</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>28,ORD-1028,2024-02-04,279.99,1,83.99,0.20,Furniture,Lounge Chair,56,Consumer,Medium,5,Delivered,FALSE,4.2,1,279.99,22.00,Net15</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>29,ORD-1029,2024-02-05,49.99,4,14.99,0.00,Electronics,Power Bank,30,Consumer,Low,2,Delivered,FALSE,4.0,4,12.50,8.50,COD</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>30,ORD-1030,2024-02-05,24.99,5,7.49,0.10,Clothing,Wool Scarf,26,Consumer,Medium,2,Delivered,FALSE,4.1,5,5.00,8.50,COD</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>31,ORD-1031,2024-02-06,119.99,1,35.99,0.05,Electronics,Gaming Headset,34,Corporate,High,3,Delivered,FALSE,4.9,1,119.99,12.00,Net30</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>32,ORD-1032,2024-02-06,69.99,2,20.99,0.10,Furniture,Night Stand,44,Home Office,Medium,3,Delivered,FALSE,4.3,2,34.99,15.00,Net15</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>33,ORD-1033,2024-02-07,109.99,1,32.99,0.15,Clothing,Athletic Shoes,29,Consumer,Medium,2,Delivered,FALSE,4.5,1,109.99,10.00,COD</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>34,ORD-1034,2024-02-07,199.99,1,59.99,0.05,Electronics,Smart Watch,38,Consumer,High,3,Delivered,FALSE,4.7,1,199.99,12.00,Net15</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>35,ORD-1035,2024-02-08,79.99,2,23.99,0.10,Electronics,Bluetooth Speaker,31,Corporate,Medium,3,Delivered,FALSE,4.4,2,39.99,10.00,Net30</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>36,ORD-1036,2024-02-08,99.99,1,29.99,0.00,Clothing,Cashmere Sweater,41,Consumer,Low,3,Returned,TRUE,2.7,1,99.99,12.00,COD</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>37,ORD-1037,2024-02-09,129.99,1,38.99,0.05,Furniture,Bookshelf,46,Home Office,Medium,4,Delivered,FALSE,4.2,1,129.99,18.00,Net15</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>38,ORD-1038,2024-02-09,99.99,1,29.99,0.10,Electronics,Mesh Router,28,Consumer,Low,2,Delivered,FALSE,4.0,1,99.99,10.00,COD</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>39,ORD-1039,2024-02-10,44.99,3,13.49,0.15,Clothing,Golf Polo,23,Consumer,Medium,2,Delivered,FALSE,4.3,3,15.00,8.50,COD</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>40,ORD-1040,2024-02-10,499.99,1,149.99,0.20,Electronics,Graphics Card,43,Corporate,High,4,Delivered,FALSE,5.0,1,499.99,18.00,Net30</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>41,ORD-1041,2024-03-01,999.99,1,299.99,0.05,Electronics,Desktop PC,50,Corporate,High,3,Delivered,FALSE,4.9,1,999.99,25.00,Net30</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>42,ORD-1042,2024-03-01,49.99,2,14.99,0.00,Clothing,Yoga Pants,27,Consumer,Medium,2,Delivered,FALSE,4.4,2,25.00,8.50,COD</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>43,ORD-1043,2024-03-02,249.99,1,74.99,0.10,Furniture,Coffee Table,55,Corporate,High,4,Delivered,FALSE,4.8,1,249.99,22.00,Net30</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>44,ORD-1044,2024-03-02,89.99,2,26.99,0.00,Electronics,Smart Speaker,34,Home Office,Medium,2,Delivered,FALSE,4.6,2,45.00,10.00,Net15</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>45,ORD-1045,2024-03-03,19.99,4,5.99,0.05,Clothing,Baseball Cap,19,Consumer,Low,2,Delivered,FALSE,3.5,4,5.00,8.50,COD</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>46,ORD-1046,2024-03-03,349.99,1,104.99,0.10,Electronics,Quadcopter,38,Consumer,High,3,Delivered,FALSE,4.9,1,349.99,18.00,COD</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>47,ORD-1047,2024-03-04,59.99,2,17.99,0.00,Furniture,Wall Mirror,42,Consumer,Medium,2,Delivered,FALSE,4.2,2,30.00,12.00,COD</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>48,ORD-1048,2024-03-04,49.99,2,14.99,0.10,Clothing,Flannel Shirt,35,Home Office,Medium,3,Delivered,FALSE,4.1,2,25.00,10.00,Net15</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>49,ORD-1049,2024-03-05,29.99,3,8.99,0.05,Electronics,Streaming Stick,24,Consumer,Low,2,Returned,TRUE,2.6,3,10.00,8.50,COD</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>50,ORD-1050,2024-03-05,29.99,4,8.99,0.00,Clothing,Leggings,22,Consumer,Medium,2,Delivered,FALSE,4.3,4,7.50,8.50,COD</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="0" t="inlineStr">
+        <is>
+          <t>Question No.</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="C1" s="0" t="inlineStr">
+        <is>
+          <t>Question Type</t>
+        </is>
+      </c>
+      <c r="D1" s="0" t="inlineStr">
+        <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="E1" s="0" t="inlineStr">
+        <is>
+          <t>Scenario/Context</t>
+        </is>
+      </c>
+      <c r="F1" s="0" t="inlineStr">
+        <is>
+          <t>Skills Tested</t>
+        </is>
+      </c>
+      <c r="G1" s="0" t="inlineStr">
+        <is>
+          <t>Option A</t>
+        </is>
+      </c>
+      <c r="H1" s="0" t="inlineStr">
+        <is>
+          <t>Option B</t>
+        </is>
+      </c>
+      <c r="I1" s="0" t="inlineStr">
+        <is>
+          <t>Option C</t>
+        </is>
+      </c>
+      <c r="J1" s="0" t="inlineStr">
+        <is>
+          <t>Option D</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>_Creating Columns from Examples</t>
+        </is>
+      </c>
+      <c r="C2" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D2" s="0" t="inlineStr">
+        <is>
+          <t>Create a column from examples to extract the brand name from Product_Name. Type examples: 'MacBook Pro' = 'Apple', 'Magic Mouse' = 'Apple', 'Designer Jeans' = 'Levi's', '27-inch Monitor' = 'Dell'</t>
+        </is>
+      </c>
+      <c r="E2" s="0" t="inlineStr"/>
+      <c r="F2" s="0" t="inlineStr"/>
+      <c r="G2" s="0" t="inlineStr"/>
+      <c r="H2" s="0" t="inlineStr"/>
+      <c r="I2" s="0" t="inlineStr"/>
+      <c r="J2" s="0" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="0" t="n">
         <v>2</v>
       </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t>_Creating Columns from Examples</t>
+        </is>
+      </c>
+      <c r="C3" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D3" s="0" t="inlineStr">
+        <is>
+          <t>Create a column from examples to extract the screen size from Product_Name. Type: 'MacBook Pro 16-inch' = '16-inch', '27-inch Monitor' = '27-inch', 'iPad Pro 12.9-inch' = '12.9-inch'</t>
+        </is>
+      </c>
+      <c r="E3" s="0" t="inlineStr"/>
+      <c r="F3" s="0" t="inlineStr"/>
+      <c r="G3" s="0" t="inlineStr"/>
+      <c r="H3" s="0" t="inlineStr"/>
+      <c r="I3" s="0" t="inlineStr"/>
+      <c r="J3" s="0" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="0" t="n">
         <v>3</v>
       </c>
+      <c r="B4" s="0" t="inlineStr">
+        <is>
+          <t>_Creating Columns from Examples</t>
+        </is>
+      </c>
+      <c r="C4" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D4" s="0" t="inlineStr">
+        <is>
+          <t>Create a column from examples to extract the product type/category from Product_Name. Type: 'MacBook Pro' = 'Laptop', 'Magic Mouse' = 'Mouse', 'Designer Jeans' = 'Jeans', '27-inch Monitor' = 'Monitor'</t>
+        </is>
+      </c>
+      <c r="E4" s="0" t="inlineStr"/>
+      <c r="F4" s="0" t="inlineStr"/>
+      <c r="G4" s="0" t="inlineStr"/>
+      <c r="H4" s="0" t="inlineStr"/>
+      <c r="I4" s="0" t="inlineStr"/>
+      <c r="J4" s="0" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="0" t="n">
         <v>4</v>
       </c>
+      <c r="B5" s="0" t="inlineStr">
+        <is>
+          <t>_Creating Columns from Examples</t>
+        </is>
+      </c>
+      <c r="C5" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D5" s="0" t="inlineStr">
+        <is>
+          <t>Create a column from examples to extract the domain name from Email_Address. Type: 'john.smith@email.com' = 'email.com', 'jane.doe@company.com' = 'company.com', 'robert.wilson@email.ca' = 'email.ca'</t>
+        </is>
+      </c>
+      <c r="E5" s="0" t="inlineStr"/>
+      <c r="F5" s="0" t="inlineStr"/>
+      <c r="G5" s="0" t="inlineStr"/>
+      <c r="H5" s="0" t="inlineStr"/>
+      <c r="I5" s="0" t="inlineStr"/>
+      <c r="J5" s="0" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="0" t="n">
         <v>5</v>
       </c>
+      <c r="B6" s="0" t="inlineStr">
+        <is>
+          <t>_Creating Columns from Examples</t>
+        </is>
+      </c>
+      <c r="C6" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D6" s="0" t="inlineStr">
+        <is>
+          <t>Create a column from examples to extract the username (text before @) from Email_Address. Type: 'john.smith@email.com' = 'john.smith', 'jane.doe@company.com' = 'jane.doe'</t>
+        </is>
+      </c>
+      <c r="E6" s="0" t="inlineStr"/>
+      <c r="F6" s="0" t="inlineStr"/>
+      <c r="G6" s="0" t="inlineStr"/>
+      <c r="H6" s="0" t="inlineStr"/>
+      <c r="I6" s="0" t="inlineStr"/>
+      <c r="J6" s="0" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="0" t="n">
         <v>6</v>
       </c>
+      <c r="B7" s="0" t="inlineStr">
+        <is>
+          <t>_Creating Columns from Examples</t>
+        </is>
+      </c>
+      <c r="C7" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D7" s="0" t="inlineStr">
+        <is>
+          <t>Create a column from examples to calculate Profit_Margin as (Profit / Sales_Amount) * 100. Type examples: 1299.99 sales, 389.99 profit = '30%', 79.99 sales, 23.99 profit = '30%'</t>
+        </is>
+      </c>
+      <c r="E7" s="0" t="inlineStr"/>
+      <c r="F7" s="0" t="inlineStr"/>
+      <c r="G7" s="0" t="inlineStr"/>
+      <c r="H7" s="0" t="inlineStr"/>
+      <c r="I7" s="0" t="inlineStr"/>
+      <c r="J7" s="0" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="0" t="n">
         <v>7</v>
       </c>
+      <c r="B8" s="0" t="inlineStr">
+        <is>
+          <t>_Creating Columns from Examples</t>
+        </is>
+      </c>
+      <c r="C8" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D8" s="0" t="inlineStr">
+        <is>
+          <t>Create a column from examples to create a combined field 'Product - Category' in format: 'MacBook Pro (Electronics)'. Type examples from Product_Name and Category</t>
+        </is>
+      </c>
+      <c r="E8" s="0" t="inlineStr"/>
+      <c r="F8" s="0" t="inlineStr"/>
+      <c r="G8" s="0" t="inlineStr"/>
+      <c r="H8" s="0" t="inlineStr"/>
+      <c r="I8" s="0" t="inlineStr"/>
+      <c r="J8" s="0" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="0" t="n">
         <v>8</v>
       </c>
+      <c r="B9" s="0" t="inlineStr">
+        <is>
+          <t>_Creating Columns from Examples</t>
+        </is>
+      </c>
+      <c r="C9" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D9" s="0" t="inlineStr">
+        <is>
+          <t>Create a column from examples to extract the year from Order_Date. Type: '2024-01-05' = '2024', '2024-01-06' = '2024'</t>
+        </is>
+      </c>
+      <c r="E9" s="0" t="inlineStr"/>
+      <c r="F9" s="0" t="inlineStr"/>
+      <c r="G9" s="0" t="inlineStr"/>
+      <c r="H9" s="0" t="inlineStr"/>
+      <c r="I9" s="0" t="inlineStr"/>
+      <c r="J9" s="0" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="0" t="n">
         <v>9</v>
       </c>
+      <c r="B10" s="0" t="inlineStr">
+        <is>
+          <t>_Creating Columns from Examples</t>
+        </is>
+      </c>
+      <c r="C10" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D10" s="0" t="inlineStr">
+        <is>
+          <t>Create a column from examples to extract the month name from Order_Date. Type: '2024-01-05' = 'January', '2024-02-01' = 'February'</t>
+        </is>
+      </c>
+      <c r="E10" s="0" t="inlineStr"/>
+      <c r="F10" s="0" t="inlineStr"/>
+      <c r="G10" s="0" t="inlineStr"/>
+      <c r="H10" s="0" t="inlineStr"/>
+      <c r="I10" s="0" t="inlineStr"/>
+      <c r="J10" s="0" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="0" t="n">
         <v>10</v>
       </c>
+      <c r="B11" s="0" t="inlineStr">
+        <is>
+          <t>_Creating Columns from Examples</t>
+        </is>
+      </c>
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D11" s="0" t="inlineStr">
+        <is>
+          <t>Create a column from examples to extract the quarter from Order_Date. Type: '2024-01-05' = 'Q1', '2024-04-01' = 'Q2', '2024-07-01' = 'Q3', '2024-10-01' = 'Q4'</t>
+        </is>
+      </c>
+      <c r="E11" s="0" t="inlineStr"/>
+      <c r="F11" s="0" t="inlineStr"/>
+      <c r="G11" s="0" t="inlineStr"/>
+      <c r="H11" s="0" t="inlineStr"/>
+      <c r="I11" s="0" t="inlineStr"/>
+      <c r="J11" s="0" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="0" t="n">
         <v>11</v>
       </c>
+      <c r="B12" s="0" t="inlineStr">
+        <is>
+          <t>_Creating Columns from Examples</t>
+        </is>
+      </c>
+      <c r="C12" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D12" s="0" t="inlineStr">
+        <is>
+          <t>Create a column from examples to create a sales tier based on Sales_Amount. Type: 1299.99 = 'Premium', 299.99 = 'Standard', 79.99 = 'Economy', 19.99 = 'Budget'</t>
+        </is>
+      </c>
+      <c r="E12" s="0" t="inlineStr"/>
+      <c r="F12" s="0" t="inlineStr"/>
+      <c r="G12" s="0" t="inlineStr"/>
+      <c r="H12" s="0" t="inlineStr"/>
+      <c r="I12" s="0" t="inlineStr"/>
+      <c r="J12" s="0" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="0" t="n">
         <v>12</v>
       </c>
+      <c r="B13" s="0" t="inlineStr">
+        <is>
+          <t>_Creating Columns from Examples</t>
+        </is>
+      </c>
+      <c r="C13" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D13" s="0" t="inlineStr">
+        <is>
+          <t>Create a column from examples to extract the first word from Full_Name. Type: 'Smith, John' = 'John', 'Doe, Jane' = 'Jane', 'Wilson, Robert' = 'Robert'</t>
+        </is>
+      </c>
+      <c r="E13" s="0" t="inlineStr"/>
+      <c r="F13" s="0" t="inlineStr"/>
+      <c r="G13" s="0" t="inlineStr"/>
+      <c r="H13" s="0" t="inlineStr"/>
+      <c r="I13" s="0" t="inlineStr"/>
+      <c r="J13" s="0" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="0" t="n">
         <v>13</v>
       </c>
+      <c r="B14" s="0" t="inlineStr">
+        <is>
+          <t>_Creating Columns from Examples</t>
+        </is>
+      </c>
+      <c r="C14" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D14" s="0" t="inlineStr">
+        <is>
+          <t>Create a column from examples to extract the last word from Full_Name. Type: 'Smith, John' = 'Smith', 'Doe, Jane' = 'Doe', 'Wilson, Robert' = 'Wilson'</t>
+        </is>
+      </c>
+      <c r="E14" s="0" t="inlineStr"/>
+      <c r="F14" s="0" t="inlineStr"/>
+      <c r="G14" s="0" t="inlineStr"/>
+      <c r="H14" s="0" t="inlineStr"/>
+      <c r="I14" s="0" t="inlineStr"/>
+      <c r="J14" s="0" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="0" t="n">
         <v>14</v>
       </c>
+      <c r="B15" s="0" t="inlineStr">
+        <is>
+          <t>_Creating Columns from Examples</t>
+        </is>
+      </c>
+      <c r="C15" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D15" s="0" t="inlineStr">
+        <is>
+          <t>Create a column from examples to create a customer greeting: 'Dear [First_Name]' from extracted first name. Type examples after first name extraction</t>
+        </is>
+      </c>
+      <c r="E15" s="0" t="inlineStr"/>
+      <c r="F15" s="0" t="inlineStr"/>
+      <c r="G15" s="0" t="inlineStr"/>
+      <c r="H15" s="0" t="inlineStr"/>
+      <c r="I15" s="0" t="inlineStr"/>
+      <c r="J15" s="0" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="0" t="n">
         <v>15</v>
       </c>
+      <c r="B16" s="0" t="inlineStr">
+        <is>
+          <t>_Creating Columns from Examples</t>
+        </is>
+      </c>
+      <c r="C16" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D16" s="0" t="inlineStr">
+        <is>
+          <t>Create a column from examples to calculate total cost: Quantity * Unit_Price. Type examples for first few rows</t>
+        </is>
+      </c>
+      <c r="E16" s="0" t="inlineStr"/>
+      <c r="F16" s="0" t="inlineStr"/>
+      <c r="G16" s="0" t="inlineStr"/>
+      <c r="H16" s="0" t="inlineStr"/>
+      <c r="I16" s="0" t="inlineStr"/>
+      <c r="J16" s="0" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="0" t="n">
         <v>16</v>
       </c>
+      <c r="B17" s="0" t="inlineStr">
+        <is>
+          <t>_Creating Columns from Examples</t>
+        </is>
+      </c>
+      <c r="C17" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D17" s="0" t="inlineStr">
+        <is>
+          <t>Create a column from examples to extract the shipping region from Address. Type: 'Chicago IL' = 'Midwest', 'Houston TX' = 'South', 'New York NY' = 'Northeast', 'Los Angeles CA' = 'West'</t>
+        </is>
+      </c>
+      <c r="E17" s="0" t="inlineStr"/>
+      <c r="F17" s="0" t="inlineStr"/>
+      <c r="G17" s="0" t="inlineStr"/>
+      <c r="H17" s="0" t="inlineStr"/>
+      <c r="I17" s="0" t="inlineStr"/>
+      <c r="J17" s="0" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="0" t="n">
         <v>17</v>
       </c>
+      <c r="B18" s="0" t="inlineStr">
+        <is>
+          <t>_Creating Columns from Examples</t>
+        </is>
+      </c>
+      <c r="C18" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D18" s="0" t="inlineStr">
+        <is>
+          <t>Create a column from examples to extract the file type from File_Name. Type: 'sales_report_2024_01_05.csv' = 'CSV', 'january_sales_2024.csv' = 'CSV'</t>
+        </is>
+      </c>
+      <c r="E18" s="0" t="inlineStr"/>
+      <c r="F18" s="0" t="inlineStr"/>
+      <c r="G18" s="0" t="inlineStr"/>
+      <c r="H18" s="0" t="inlineStr"/>
+      <c r="I18" s="0" t="inlineStr"/>
+      <c r="J18" s="0" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="0" t="n">
         <v>18</v>
       </c>
+      <c r="B19" s="0" t="inlineStr">
+        <is>
+          <t>_Creating Columns from Examples</t>
+        </is>
+      </c>
+      <c r="C19" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D19" s="0" t="inlineStr">
+        <is>
+          <t>Create a column from examples to extract the ID prefix from ID_Number. Type: 'ID-001-ABC-2024' = 'ID', 'CUST-001' = 'CUST', 'ORD-1001' = 'ORD'</t>
+        </is>
+      </c>
+      <c r="E19" s="0" t="inlineStr"/>
+      <c r="F19" s="0" t="inlineStr"/>
+      <c r="G19" s="0" t="inlineStr"/>
+      <c r="H19" s="0" t="inlineStr"/>
+      <c r="I19" s="0" t="inlineStr"/>
+      <c r="J19" s="0" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="0" t="n">
         <v>19</v>
       </c>
+      <c r="B20" s="0" t="inlineStr">
+        <is>
+          <t>_Creating Columns from Examples</t>
+        </is>
+      </c>
+      <c r="C20" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D20" s="0" t="inlineStr">
+        <is>
+          <t>Create a column from examples to categorize feedback sentiment. Type: 'Excellent product!' = 'Positive', 'Very comfortable' = 'Positive', 'Good value for money' = 'Positive', 'Not working' = 'Negative'</t>
+        </is>
+      </c>
+      <c r="E20" s="0" t="inlineStr"/>
+      <c r="F20" s="0" t="inlineStr"/>
+      <c r="G20" s="0" t="inlineStr"/>
+      <c r="H20" s="0" t="inlineStr"/>
+      <c r="I20" s="0" t="inlineStr"/>
+      <c r="J20" s="0" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="0" t="inlineStr">
+        <is>
+          <t>_Creating Columns from Examples</t>
+        </is>
+      </c>
+      <c r="C21" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D21" s="0" t="inlineStr">
+        <is>
+          <t>Create a column from examples to create a product URL slug from Product_Name. Type: 'MacBook Pro' = 'macbook-pro', 'Magic Mouse' = 'magic-mouse', 'Designer Jeans' = 'designer-jeans'</t>
+        </is>
+      </c>
+      <c r="E21" s="0" t="inlineStr"/>
+      <c r="F21" s="0" t="inlineStr"/>
+      <c r="G21" s="0" t="inlineStr"/>
+      <c r="H21" s="0" t="inlineStr"/>
+      <c r="I21" s="0" t="inlineStr"/>
+      <c r="J21" s="0" t="inlineStr"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>